--- a/outputs/evaluation/architecture/validation/gemini-3-5/CF_M01/run_2/CF_M01_arch_eval.xlsx
+++ b/outputs/evaluation/architecture/validation/gemini-3-5/CF_M01/run_2/CF_M01_arch_eval.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -440,6 +440,11 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>f1</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>mean semantic meaning</t>
         </is>
       </c>
@@ -456,7 +461,10 @@
       <c r="C2" t="n">
         <v>0.7</v>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" t="n">
+        <v>0.6087</v>
+      </c>
+      <c r="E2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -475,6 +483,9 @@
         <v>0.75</v>
       </c>
       <c r="D3" t="n">
+        <v>0.6316000000000001</v>
+      </c>
+      <c r="E3" t="n">
         <v>0.9665</v>
       </c>
     </row>
@@ -491,6 +502,9 @@
         <v>0.5</v>
       </c>
       <c r="D4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E4" t="n">
         <v>0.9034</v>
       </c>
     </row>
@@ -1224,13 +1238,11 @@
           <t>['AU_13']</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
           <t>AU_16</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
           <t>AWS RDS</t>
@@ -1254,13 +1266,11 @@
           <t>CF_M01_AU15</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
           <t>CF_M01_AU35</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1306,13 +1316,11 @@
           <t>['AU_43']</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
           <t>AU_36</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
           <t>REST</t>
@@ -1336,13 +1344,11 @@
           <t>CF_M01_AU24</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr">
         <is>
           <t>CF_M01_AU04</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1388,13 +1394,11 @@
           <t>['AU_04']</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
           <t>AU_09</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
           <t>Core Service</t>
@@ -1418,13 +1422,11 @@
           <t>CF_M01_AU06</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr">
         <is>
           <t>CF_M01_AU11</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1445,7 +1447,6 @@
       <c r="D5" t="n">
         <v>0.8786</v>
       </c>
-      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1461,15 +1462,11 @@
           <t>42</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
           <t>AU_44</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1488,7 +1485,6 @@
           <t>CF_M01_AU05, CF_M01_AU10</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr">
         <is>
           <t>CF_M01_AU25</t>
@@ -1519,7 +1515,6 @@
       <c r="D6" t="n">
         <v>0.8815</v>
       </c>
-      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1540,7 +1535,6 @@
           <t>['AU_11', 'AU_41']</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
           <t>AU_46</t>
@@ -1551,7 +1545,6 @@
           <t>api player, player</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1570,7 +1563,6 @@
           <t>CF_M01_AU27, CF_M01_AU13</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr">
         <is>
           <t>CF_M01_AU28</t>
@@ -1626,13 +1618,11 @@
           <t>['AU_05']</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
           <t>AU_14</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
           <t>AWS cloud services set</t>
@@ -1658,13 +1648,11 @@
           <t>CF_M01_AU07</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr">
         <is>
           <t>CF_M01_AU16</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1710,13 +1698,11 @@
           <t>['AU_03']</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
           <t>AU_06</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
           <t>Web platform interface</t>
@@ -1740,13 +1726,11 @@
           <t>CF_M01_AU05</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr">
         <is>
           <t>CF_M01_AU08</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1792,13 +1776,11 @@
           <t>['AU_04']</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
           <t>AU_08</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
           <t>API Gateway Service</t>
@@ -1822,13 +1804,11 @@
           <t>CF_M01_AU06</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr">
         <is>
           <t>CF_M01_AU10</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1849,7 +1829,6 @@
       <c r="D10" t="n">
         <v>0.9262</v>
       </c>
-      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1870,7 +1849,6 @@
           <t>['AU_12', 'AU_41']</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
           <t>AU_47</t>
@@ -1881,7 +1859,6 @@
           <t>web socket, player</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1900,7 +1877,6 @@
           <t>CF_M01_AU27, CF_M01_AU14</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr">
         <is>
           <t>CF_M01_AU29</t>
@@ -1931,7 +1907,6 @@
       <c r="D11" t="n">
         <v>0.9275</v>
       </c>
-      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1952,7 +1927,6 @@
           <t>['AU_03', 'AU_04']</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
           <t>AU_43</t>
@@ -1963,7 +1937,6 @@
           <t>capa de presentació, capa de negoci</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1982,7 +1955,6 @@
           <t>CF_M01_AU01, CF_M01_AU02</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr">
         <is>
           <t>CF_M01_AU24</t>
@@ -2033,7 +2005,6 @@
           <t>43</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
           <t>Architectural Pattern</t>
@@ -2044,7 +2015,6 @@
           <t>P_03</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
           <t>API Gateway</t>
@@ -2068,13 +2038,11 @@
           <t>CF_M01_P03</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr">
         <is>
           <t>CF_M01_P04</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2120,13 +2088,11 @@
           <t>['AU_14']</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
           <t>AU_18</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
           <t>Amazon DynamoDB</t>
@@ -2150,13 +2116,11 @@
           <t>CF_M01_AU16</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr">
         <is>
           <t>CF_M01_AU18</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2202,13 +2166,11 @@
           <t>['AU_04']</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
           <t>AU_11</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
           <t>Api Player</t>
@@ -2232,13 +2194,11 @@
           <t>CF_M01_AU06</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr">
         <is>
           <t>CF_M01_AU13</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2284,13 +2244,11 @@
           <t>['AU_13', 'AU_48']</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
           <t>AU_15</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
           <t>MySQL</t>
@@ -2314,13 +2272,11 @@
           <t>CF_M01_AU15</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr">
         <is>
           <t>CF_M01_AU32</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2361,14 +2317,11 @@
           <t>8</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
           <t>AU_41</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
           <t>Player</t>
@@ -2387,14 +2340,11 @@
       <c r="P16" t="n">
         <v>8</v>
       </c>
-      <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr">
         <is>
           <t>CF_M01_AU27</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2435,14 +2385,11 @@
           <t>49</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
           <t>AU_24</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
           <t>Amazon Athena</t>
@@ -2466,13 +2413,11 @@
           <t>CF_M01_AU16</t>
         </is>
       </c>
-      <c r="R17" t="inlineStr"/>
       <c r="S17" t="inlineStr">
         <is>
           <t>CF_M01_AU20</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2518,13 +2463,11 @@
           <t>['AU_43', 'AU_44']</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
           <t>AU_35</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
           <t>HTTP</t>
@@ -2548,13 +2491,11 @@
           <t>CF_M01_AU24, CF_M01_AU25</t>
         </is>
       </c>
-      <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr">
         <is>
           <t>CF_M01_AU03</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2595,14 +2536,11 @@
           <t>46</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
           <t>AU_19</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
           <t>NestJS</t>
@@ -2626,13 +2564,11 @@
           <t>CF_M01_AU02</t>
         </is>
       </c>
-      <c r="R19" t="inlineStr"/>
       <c r="S19" t="inlineStr">
         <is>
           <t>CF_M01_AU33</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2673,14 +2609,11 @@
           <t>41</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
           <t>AU_01</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
           <t>Client</t>
@@ -2704,13 +2637,11 @@
           <t>CF_M01_P01</t>
         </is>
       </c>
-      <c r="R20" t="inlineStr"/>
       <c r="S20" t="inlineStr">
         <is>
           <t>CF_M01_AU01</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2756,13 +2687,11 @@
           <t>['AU_04']</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
           <t>AU_12</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
           <t>Web Socket</t>
@@ -2786,13 +2715,11 @@
           <t>CF_M01_AU06</t>
         </is>
       </c>
-      <c r="R21" t="inlineStr"/>
       <c r="S21" t="inlineStr">
         <is>
           <t>CF_M01_AU14</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2838,13 +2765,11 @@
           <t>['AU_14']</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
           <t>AU_17</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
           <t>Amazon S3</t>
@@ -2868,13 +2793,11 @@
           <t>CF_M01_AU16</t>
         </is>
       </c>
-      <c r="R22" t="inlineStr"/>
       <c r="S22" t="inlineStr">
         <is>
           <t>CF_M01_AU17</t>
         </is>
       </c>
-      <c r="T22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2915,14 +2838,11 @@
           <t>49</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
           <t>AU_25</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
           <t>AWS Glue</t>
@@ -2946,13 +2866,11 @@
           <t>CF_M01_AU16</t>
         </is>
       </c>
-      <c r="R23" t="inlineStr"/>
       <c r="S23" t="inlineStr">
         <is>
           <t>CF_M01_AU21</t>
         </is>
       </c>
-      <c r="T23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2993,14 +2911,11 @@
           <t>41</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
           <t>AU_02</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
           <t>Server</t>
@@ -3024,13 +2939,11 @@
           <t>CF_M01_P01</t>
         </is>
       </c>
-      <c r="R24" t="inlineStr"/>
       <c r="S24" t="inlineStr">
         <is>
           <t>CF_M01_AU02</t>
         </is>
       </c>
-      <c r="T24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -3071,14 +2984,11 @@
           <t>50</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
           <t>AU_26</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
           <t>Kinesis Data Streams</t>
@@ -3104,13 +3014,11 @@
           <t>CF_M01_AU16</t>
         </is>
       </c>
-      <c r="R25" t="inlineStr"/>
       <c r="S25" t="inlineStr">
         <is>
           <t>CF_M01_AU22</t>
         </is>
       </c>
-      <c r="T25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -3151,14 +3059,11 @@
           <t>41</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
           <t>P_01</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
           <t>Client-Server</t>
@@ -3177,14 +3082,11 @@
       <c r="P26" t="n">
         <v>41</v>
       </c>
-      <c r="Q26" t="inlineStr"/>
-      <c r="R26" t="inlineStr"/>
       <c r="S26" t="inlineStr">
         <is>
           <t>CF_M01_P01</t>
         </is>
       </c>
-      <c r="T26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -3225,14 +3127,11 @@
           <t>46</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
           <t>AU_21</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
           <t>TypeScript</t>
@@ -3256,13 +3155,11 @@
           <t>CF_M01_AU33</t>
         </is>
       </c>
-      <c r="R27" t="inlineStr"/>
       <c r="S27" t="inlineStr">
         <is>
           <t>CF_M01_AU34</t>
         </is>
       </c>
-      <c r="T27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -3303,14 +3200,11 @@
           <t>51</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr">
         <is>
           <t>AU_27</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
           <t>Kinesis Data Firehose</t>
@@ -3334,13 +3228,11 @@
           <t>CF_M01_AU16</t>
         </is>
       </c>
-      <c r="R28" t="inlineStr"/>
       <c r="S28" t="inlineStr">
         <is>
           <t>CF_M01_AU23</t>
         </is>
       </c>
-      <c r="T28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -3386,13 +3278,11 @@
           <t>['AU_45']</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
         <is>
           <t>AU_37</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
           <t>TCP</t>
@@ -3416,13 +3306,11 @@
           <t>CF_M01_AU26</t>
         </is>
       </c>
-      <c r="R29" t="inlineStr"/>
       <c r="S29" t="inlineStr">
         <is>
           <t>CF_M01_AU31</t>
         </is>
       </c>
-      <c r="T29" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3496,7 +3384,6 @@
           <t>Capa de presentació</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>Capa de presentació: És la capa que s'encarrega de mostrar la informació a l'usuari.</t>
@@ -3532,7 +3419,6 @@
           <t>Capa de negoci</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>Capa de negoci: Aquesta capa és el nucli de l'aplicació, que s'encarrega de processar tota la informació.</t>
@@ -3568,7 +3454,6 @@
           <t>Capa de dades</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>Capa de dades: És la capa que s'encarrega d'emmagatzemar totes les dades.</t>
@@ -3604,7 +3489,6 @@
           <t>plataforma mòbil</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
           <t>En el cas d'aquesta capa, es pot observar de què està formada per la interfície de la plataforma web i la plataforma mòbil de Waapiti.</t>
@@ -3640,7 +3524,6 @@
           <t>mòdul analític</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
           <t>Aquests components vindrien a ser, l'Api Gateway, el Core i el mòdul analític.</t>
@@ -3676,7 +3559,6 @@
           <t>Base de dades</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
           <t>La base de dades utilitzada és una base de dades MySQL que s'encarrega d'emmagatzemar totes les dades necessàries per al funcionament del sistema.</t>
@@ -3712,7 +3594,6 @@
           <t>NodeJS</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
           <t>Aquest framework és un framework de NodeJS que té com a funció principal la creació d'aplicacions de backend.</t>
@@ -3748,7 +3629,6 @@
           <t>JavaScript</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
           <t>Aquest llenguatge de programació que està construït a un nivell superior de JavaScript, és a dir, que estén la sintaxi de JavaScript.</t>
@@ -3784,7 +3664,6 @@
           <t>Infraestructura AWS</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
           <t>És el conjunt de serveis de computació en el núvol que permet la creació d'aplicacions escalables i altament disponibles.</t>
@@ -3820,7 +3699,6 @@
           <t>AWS Cloud Development</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
           <t>Per poder desenvolupar tota la infraestructura necessària per al projecte s'ha fet ús de l'AWS Cloud Development, també anomenat AWS CDK.</t>
@@ -3856,7 +3734,6 @@
           <t>AWS CDK</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
           <t>Per poder desenvolupar tota la infraestructura necessària per al projecte s'ha fet ús de l'AWS Cloud Development, també anomenat AWS CDK.</t>
@@ -3892,7 +3769,6 @@
           <t>Python</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>Com es pot veure en la figura 11.5 permet fer ús dels llenguatges de programació TypeScript, JavaScript, Python, Java i C#/.NET</t>
@@ -3928,7 +3804,6 @@
           <t>Java</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>Com es pot veure en la figura 11.5 permet fer ús dels llenguatges de programació TypeScript, JavaScript, Python, Java i C#/.NET</t>
@@ -3964,7 +3839,6 @@
           <t>C#/.NET</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>Com es pot veure en la figura 11.5 permet fer ús dels llenguatges de programació TypeScript, JavaScript, Python, Java i C#/.NET</t>
@@ -4000,7 +3874,6 @@
           <t>AWS CloudFormation</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
           <t>AWS CloudFormation est un servei d'Amazon que ajuda a configurar els recursos d'AWS.</t>
@@ -4036,7 +3909,6 @@
           <t>CloudFormation</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
           <t>AWS CloudFormation est un servei d'Amazon que ajuda a configurar els recursos d'AWS.</t>
@@ -4072,7 +3944,6 @@
           <t>pantalles digitals</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
           <t>Waapiti és una empresa especialitzada en donar solucions de senyalització digital [1], que fa ús de les pantalles digitals com vindrien a ser monitors o pantalles LED per a la visualització de continguts de forma dinàmica</t>
@@ -4108,7 +3979,6 @@
           <t>monitors</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
           <t>Waapiti és una empresa especialitzada en donar solucions de senyalització digital [1], que fa ús de les pantalles digitals com vindrien a ser monitors o pantalles LED per a la visualització de continguts de forma dinàmica</t>
@@ -4144,7 +4014,6 @@
           <t>pantalles LED</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
           <t>Waapiti és una empresa especialitzada en donar solucions de senyalització digital [1], que fa ús de les pantalles digitals com vindrien a ser monitors o pantalles LED per a la visualització de continguts de forma dinàmica</t>
@@ -4175,7 +4044,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
           <t>client, server</t>
@@ -4211,7 +4079,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
           <t>api gateway, core</t>
@@ -4227,7 +4094,6 @@
           <t>CF_M01_AU24</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
         <v>0.7436</v>
       </c>
@@ -4243,7 +4109,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
           <t>core, base de dades</t>
@@ -4279,7 +4144,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
           <t>mòdul analític, conjunt de serveis cloud aws</t>
@@ -4320,7 +4184,6 @@
           <t>3 Layers</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
           <t>Pel model client-servidor s'utilitza l'arquitectura de 3 capes, on el sistema es devidiex en 3 capes, la capa de presentació, la capa de negoci i la capa de dades.</t>
@@ -4412,7 +4275,6 @@
           <t>Presentation Layer</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>It is the layer that is responsible for displaying information to the user. In this project, it is the visual interface of the Waapiti platform.</t>
@@ -4423,7 +4285,6 @@
           <t>AU_44</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
         <v>0.7416</v>
       </c>
@@ -4444,7 +4305,6 @@
           <t>Business Layer</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>This layer is the core of the application, which is responsible for processing all the information. In our context, it is the software that is responsible for processing user requests.</t>
@@ -4480,7 +4340,6 @@
           <t>Data Layer</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>It is the layer that is responsible for storing all the data. In our case, it would be the database and AWS storage services.</t>
@@ -4516,7 +4375,6 @@
           <t>Waapiti Mobile Platform</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
           <t>In the case of this layer, you can see that it is made up of the interface of the web platform and the Waapiti mobile platform.</t>
@@ -4547,7 +4405,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
           <t>presentation layer, business layer</t>
@@ -4563,7 +4420,6 @@
           <t>AU_44</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
         <v>0.7695</v>
       </c>
@@ -4579,7 +4435,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
           <t>api gateway service, core service, analytical module</t>
@@ -4620,7 +4475,6 @@
           <t>Analytical module</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
           <t>Its main function is to obtain and process data from playlogs, connections and platform actions. This service mainly interacts with cloud services, although it also interacts to a lesser extent with the database.</t>
@@ -4656,7 +4510,6 @@
           <t>SQL database</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
           <t>As can be seen in Figure 9.1, the data layer is made up of AWS cloud services and the database. [...] The database used is a MySQL database that is responsible for storing all the data necessary for the operation of the system. This database is implemented in the RDS service [30], which is a distributed relational database service from AWS.</t>
@@ -4687,7 +4540,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
           <t>analytical module, aws cloud services set, sql database</t>
@@ -4723,7 +4575,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
           <t>core service, sql database, aws cloud services set</t>
@@ -4764,7 +4615,6 @@
           <t>Three Layers</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
           <t>The client-server model uses a 3-layer architecture, where the system is divided into 3 layers.</t>
@@ -4800,7 +4650,6 @@
           <t>Service-oriented</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>Both the business layer and the data layer are divided into several different services</t>
